--- a/ДЗ.xlsx
+++ b/ДЗ.xlsx
@@ -5,10 +5,10 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\demsh\Desktop\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Learning\OAP\CppProjects\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DA6610E2-1F4B-48F0-BB24-3D06EF34C613}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CF240B47-ACA3-4774-9B62-2F40DA2ECD16}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="24240" windowHeight="13140" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5" uniqueCount="5">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="7" uniqueCount="7">
   <si>
     <t>Дата</t>
   </si>
@@ -43,6 +43,12 @@
   </si>
   <si>
     <t>Отличие Российской и Британской школ 10 предложений</t>
+  </si>
+  <si>
+    <t>ААС</t>
+  </si>
+  <si>
+    <t>Перерисовать схемы с лекции в тетрадь</t>
   </si>
 </sst>
 </file>
@@ -147,7 +153,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="7">
+  <cellXfs count="8">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
@@ -157,6 +163,7 @@
     <xf numFmtId="16" fontId="0" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
+    <xf numFmtId="16" fontId="0" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Обычный" xfId="0" builtinId="0"/>
@@ -468,9 +475,15 @@
       </c>
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A3" s="3"/>
-      <c r="B3" s="3"/>
-      <c r="C3" s="3"/>
+      <c r="A3" s="7">
+        <v>46295</v>
+      </c>
+      <c r="B3" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="C3" s="3" t="s">
+        <v>6</v>
+      </c>
     </row>
     <row r="4" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A4" s="3"/>
